--- a/02_Corporate_Finance/instances/public_microsoft_2024.xlsx
+++ b/02_Corporate_Finance/instances/public_microsoft_2024.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="285">
   <si>
     <t xml:space="preserve">Microsoft FY2024 treasury and capital allocation</t>
   </si>
@@ -646,6 +646,9 @@
   </si>
   <si>
     <t xml:space="preserve">Implied value/share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast base (IS!E5)</t>
   </si>
   <si>
     <t xml:space="preserve">Comparable Companies</t>
@@ -1660,36 +1663,36 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15"/>
       <c r="B4" s="15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C5" s="18" t="n">
         <v>0</v>
@@ -1712,7 +1715,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C6" s="18" t="n">
         <v>0</v>
@@ -1735,7 +1738,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C7" s="18" t="n">
         <v>0</v>
@@ -1758,7 +1761,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C8" s="18" t="n">
         <v>0</v>
@@ -1781,7 +1784,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C9" s="18" t="n">
         <v>0</v>
@@ -1804,7 +1807,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C10" s="18" t="n">
         <v>0</v>
@@ -1827,7 +1830,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C11" s="18" t="n">
         <v>0</v>
@@ -1850,7 +1853,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C13" s="28" t="n">
         <f aca="false">MEDIAN(C5:C12)</f>
@@ -1903,12 +1906,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="32" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C4" s="33" t="n">
         <v>0.015</v>
@@ -1931,19 +1934,19 @@
         <v>0.08</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1951,19 +1954,19 @@
         <v>0.09</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1971,19 +1974,19 @@
         <v>0.1</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1991,19 +1994,19 @@
         <v>0.11</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2011,19 +2014,19 @@
         <v>0.12</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -2054,7 +2057,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2063,33 +2066,33 @@
         <v>92</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="34" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2182,26 +2185,26 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C5" s="18" t="n">
         <v>34704</v>
@@ -2212,7 +2215,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C6" s="18" t="n">
         <v>118548</v>
@@ -2223,7 +2226,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C7" s="18" t="n">
         <v>44477</v>
@@ -2234,7 +2237,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C8" s="18" t="n">
         <v>21771</v>
@@ -2245,7 +2248,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C9" s="18" t="n">
         <v>17254</v>
@@ -2256,7 +2259,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C10" s="18" t="n">
         <v>24395</v>
@@ -2267,7 +2270,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C11" s="18" t="n">
         <v>29070</v>
@@ -2278,7 +2281,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C12" s="18" t="n">
         <v>71802</v>
@@ -2300,7 +2303,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C14" s="18" t="n">
         <v>1700</v>
@@ -2311,7 +2314,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C15" s="18" t="n">
         <v>20000</v>
@@ -2322,7 +2325,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C16" s="30" t="n">
         <v>2</v>
@@ -2333,7 +2336,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="0" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C17" s="30" t="n">
         <v>10</v>
@@ -2344,7 +2347,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C21" s="22" t="n">
         <f aca="false">C5+C6-C7-C8-C9+C10-C11</f>
@@ -2357,7 +2360,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="0" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C22" s="22" t="n">
         <f aca="false">C12+C10-C11</f>
@@ -2370,7 +2373,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="0" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C23" s="22" t="n">
         <f aca="false">C22-C21</f>
@@ -2383,7 +2386,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C24" s="35" t="n">
         <f aca="false">IFERROR(C23/C13,0)</f>
@@ -2396,7 +2399,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="0" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C25" s="35" t="n">
         <f aca="false">IFERROR(C13/C14,0)</f>
@@ -2409,7 +2412,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="0" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C26" s="22" t="n">
         <f aca="false">MAX(0,C15-C21)</f>
@@ -2422,7 +2425,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="0" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C27" s="22" t="n">
         <f aca="false">C6-C7</f>
@@ -2435,7 +2438,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C28" s="22" t="n">
         <f aca="false">C8+C9</f>
@@ -2473,26 +2476,26 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="15" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C5" s="22" t="n">
         <f aca="false">'Treasury &amp; Liquidity'!C6</f>
@@ -2503,12 +2506,12 @@
         <v>118548</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C6" s="22" t="n">
         <f aca="false">'Treasury &amp; Liquidity'!C7</f>
@@ -2519,12 +2522,12 @@
         <v>44477</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C7" s="22" t="n">
         <f aca="false">'Treasury &amp; Liquidity'!C8</f>
@@ -2535,12 +2538,12 @@
         <v>21771</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C8" s="22" t="n">
         <f aca="false">'Treasury &amp; Liquidity'!C9</f>
@@ -2551,12 +2554,12 @@
         <v>17254</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C9" s="22" t="n">
         <f aca="false">'Treasury &amp; Liquidity'!C11</f>
@@ -2567,12 +2570,12 @@
         <v>29070</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C10" s="22" t="n">
         <f aca="false">'Treasury &amp; Liquidity'!C10</f>
@@ -2583,12 +2586,12 @@
         <v>24395</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C13" s="22" t="n">
         <f aca="false">MAX(0,C7+C8-C5+C6)</f>
@@ -2601,7 +2604,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C14" s="22" t="n">
         <f aca="false">'Treasury &amp; Liquidity'!C21-('Treasury &amp; Liquidity'!C5+'Treasury &amp; Liquidity'!C6-'Treasury &amp; Liquidity'!C7-'Treasury &amp; Liquidity'!C8-'Treasury &amp; Liquidity'!C9+'Treasury &amp; Liquidity'!C10-'Treasury &amp; Liquidity'!C11)</f>
@@ -2639,26 +2642,26 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C5" s="22" t="n">
         <f aca="false">'Treasury &amp; Liquidity'!C21</f>
@@ -2669,12 +2672,12 @@
         <v>43947</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C6" s="35" t="n">
         <f aca="false">'Treasury &amp; Liquidity'!C24</f>
@@ -2685,12 +2688,12 @@
         <v>0.211882998171846</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C7" s="35" t="n">
         <f aca="false">'Treasury &amp; Liquidity'!C25</f>
@@ -2701,12 +2704,12 @@
         <v>64.3529411764706</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C8" s="22" t="n">
         <f aca="false">'Treasury &amp; Liquidity'!C26</f>
@@ -2717,12 +2720,12 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C9" s="22" t="n">
         <f aca="false">'Capital Allocation'!C13</f>
@@ -2733,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -2763,26 +2766,26 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="15" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>41</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C5" s="36" t="n">
         <f aca="false">'Capital Allocation'!D14</f>
@@ -2793,12 +2796,12 @@
         <v>PASS</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C6" s="36" t="n">
         <f aca="false">'Treasury &amp; Liquidity'!D22-('Treasury &amp; Liquidity'!D12+'Treasury &amp; Liquidity'!D10-'Treasury &amp; Liquidity'!D11)</f>
@@ -2809,12 +2812,12 @@
         <v>PASS</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C7" s="36" t="n">
         <f aca="false">'Treasury &amp; Liquidity'!D21-'Treasury &amp; Liquidity'!D15</f>
@@ -2825,12 +2828,12 @@
         <v>PASS</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C8" s="36" t="n">
         <f aca="false">'Treasury &amp; Liquidity'!D24</f>
@@ -2841,12 +2844,12 @@
         <v>PASS</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C9" s="36" t="n">
         <f aca="false">'Treasury &amp; Liquidity'!D25</f>
@@ -2857,12 +2860,12 @@
         <v>PASS</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C10" s="36" t="n">
         <f aca="false">'Capital Allocation'!D13</f>
@@ -2873,12 +2876,12 @@
         <v>PASS</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C12" s="37" t="str">
         <f aca="false">IF(COUNTIF(D5:D10,"FAIL")+COUNTIF(D5:D10,"BREACH")&gt;0,"BREACH",IF(COUNTIF(D5:D10,"REVIEW")&gt;0,"REVIEW","PASS"))</f>
@@ -4412,9 +4415,9 @@
       <c r="B5" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
       <c r="F5" s="19" t="n">
         <f aca="false">E5*(1+Assumptions!C5)</f>
         <v>0</v>
@@ -4436,7 +4439,7 @@
       <c r="B6" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="20"/>
+      <c r="C6" s="16"/>
       <c r="D6" s="20" t="str">
         <f aca="false">IFERROR(D5/C5-1,"-")</f>
         <v>-</v>
@@ -4466,9 +4469,9 @@
       <c r="B7" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
       <c r="F7" s="19" t="n">
         <f aca="false">F5*(1-Assumptions!C6)</f>
         <v>0</v>
@@ -4490,7 +4493,7 @@
       <c r="B8" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C8" s="19"/>
+      <c r="C8" s="18"/>
       <c r="D8" s="19" t="n">
         <f aca="false">D5-D7</f>
         <v>0</v>
@@ -4520,7 +4523,7 @@
       <c r="B9" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C9" s="20"/>
+      <c r="C9" s="16"/>
       <c r="D9" s="20" t="str">
         <f aca="false">IFERROR(D8/D5,"-")</f>
         <v>-</v>
@@ -4550,9 +4553,9 @@
       <c r="B10" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
       <c r="F10" s="19" t="n">
         <f aca="false">F5*Assumptions!C7</f>
         <v>0</v>
@@ -4574,9 +4577,9 @@
       <c r="B11" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
       <c r="F11" s="19" t="n">
         <f aca="false">F8-F10</f>
         <v>0</v>
@@ -4598,9 +4601,9 @@
       <c r="B12" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
       <c r="F12" s="20" t="str">
         <f aca="false">IFERROR(F11/F5,"-")</f>
         <v>-</v>
@@ -4622,9 +4625,9 @@
       <c r="B13" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
       <c r="F13" s="19" t="n">
         <f aca="false">F5*Assumptions!C10*Assumptions!C9</f>
         <v>0</v>
@@ -4646,9 +4649,9 @@
       <c r="B14" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
       <c r="F14" s="19" t="n">
         <f aca="false">F11-F13</f>
         <v>0</v>
@@ -4670,9 +4673,9 @@
       <c r="B15" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
       <c r="F15" s="19" t="n">
         <f aca="false">$E$15</f>
         <v>0</v>
@@ -4694,9 +4697,9 @@
       <c r="B16" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
       <c r="F16" s="19" t="n">
         <f aca="false">F14-F15</f>
         <v>0</v>
@@ -4718,9 +4721,9 @@
       <c r="B17" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
       <c r="F17" s="19" t="n">
         <f aca="false">F16*Assumptions!C8</f>
         <v>0</v>
@@ -4742,9 +4745,9 @@
       <c r="B18" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
       <c r="F18" s="19" t="n">
         <f aca="false">F16-F17</f>
         <v>0</v>
@@ -4766,9 +4769,9 @@
       <c r="B19" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
       <c r="F19" s="19" t="n">
         <f aca="false">Assumptions!C12</f>
         <v>7400.1</v>
@@ -4790,9 +4793,9 @@
       <c r="B20" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
       <c r="F20" s="19" t="n">
         <f aca="false">IFERROR(F18/F19,"-")</f>
         <v>0</v>
@@ -5294,7 +5297,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:I14"/>
+  <dimension ref="B2:I15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -5480,9 +5483,18 @@
       <c r="H14" s="0" t="s">
         <v>201</v>
       </c>
-      <c r="I14" s="28" t="n">
-        <f aca="false">I12/I13</f>
-        <v>1.13209577616357</v>
+      <c r="I14" s="28" t="str">
+        <f aca="false">IF(OR(IS!E5="",IS!E5=0),"n/a - no forecast base",I12/I13)</f>
+        <v>n/a - no forecast base</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H15" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="I15" s="2" t="str">
+        <f aca="false">IF(OR(IS!E5="",IS!E5=0),"MISSING - the DCF cannot value anything","present")</f>
+        <v>MISSING - the DCF cannot value anything</v>
       </c>
     </row>
   </sheetData>

--- a/02_Corporate_Finance/instances/public_microsoft_2024.xlsx
+++ b/02_Corporate_Finance/instances/public_microsoft_2024.xlsx
@@ -723,7 +723,7 @@
     <t xml:space="preserve">Next check</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01</t>
+    <t xml:space="preserve">2026-09-07</t>
   </si>
   <si>
     <t xml:space="preserve">Depth pass: full input accounting against recorded XBRL facts</t>
@@ -4415,24 +4415,30 @@
       <c r="B5" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
+      <c r="C5" s="18" t="n">
+        <v>198270</v>
+      </c>
+      <c r="D5" s="18" t="n">
+        <v>211915</v>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>245122</v>
+      </c>
       <c r="F5" s="19" t="n">
         <f aca="false">E5*(1+Assumptions!C5)</f>
-        <v>0</v>
+        <v>280688.957078</v>
       </c>
       <c r="G5" s="19" t="n">
         <f aca="false">F5*(1+Assumptions!D5)</f>
-        <v>0</v>
+        <v>316064.18633854</v>
       </c>
       <c r="H5" s="19" t="n">
         <f aca="false">G5*(1+Assumptions!E5)</f>
-        <v>0</v>
+        <v>349870.411709311</v>
       </c>
       <c r="I5" s="19" t="n">
         <f aca="false">H5*(1+Assumptions!F5)</f>
-        <v>0</v>
+        <v>380620.522194442</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4440,83 +4446,91 @@
         <v>128</v>
       </c>
       <c r="C6" s="16"/>
-      <c r="D6" s="20" t="str">
+      <c r="D6" s="20" t="n">
         <f aca="false">IFERROR(D5/C5-1,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E6" s="20" t="str">
+        <v>0.0688202955565642</v>
+      </c>
+      <c r="E6" s="20" t="n">
         <f aca="false">IFERROR(E5/D5-1,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F6" s="20" t="str">
+        <v>0.156699620130713</v>
+      </c>
+      <c r="F6" s="20" t="n">
         <f aca="false">IFERROR(F5/E5-1,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G6" s="20" t="str">
+        <v>0.145099</v>
+      </c>
+      <c r="G6" s="20" t="n">
         <f aca="false">IFERROR(G5/F5-1,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H6" s="20" t="str">
+        <v>0.12603</v>
+      </c>
+      <c r="H6" s="20" t="n">
         <f aca="false">IFERROR(H5/G5-1,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I6" s="20" t="str">
+        <v>0.10696</v>
+      </c>
+      <c r="I6" s="20" t="n">
         <f aca="false">IFERROR(I5/H5-1,"-")</f>
-        <v>-</v>
+        <v>0.08789</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
+      <c r="C7" s="18" t="n">
+        <v>62650</v>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>65863</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>74114</v>
+      </c>
       <c r="F7" s="19" t="n">
         <f aca="false">F5*(1-Assumptions!C6)</f>
-        <v>0</v>
+        <v>84867.9903062758</v>
       </c>
       <c r="G7" s="19" t="n">
         <f aca="false">G5*(1-Assumptions!D6)</f>
-        <v>0</v>
+        <v>95563.9031245757</v>
       </c>
       <c r="H7" s="19" t="n">
         <f aca="false">H5*(1-Assumptions!E6)</f>
-        <v>0</v>
+        <v>105785.41820278</v>
       </c>
       <c r="I7" s="19" t="n">
         <f aca="false">I5*(1-Assumptions!F6)</f>
-        <v>0</v>
+        <v>115082.898608623</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C8" s="18"/>
+      <c r="C8" s="18" t="n">
+        <v>135620</v>
+      </c>
       <c r="D8" s="19" t="n">
         <f aca="false">D5-D7</f>
-        <v>0</v>
+        <v>146052</v>
       </c>
       <c r="E8" s="19" t="n">
         <f aca="false">E5-E7</f>
-        <v>0</v>
+        <v>171008</v>
       </c>
       <c r="F8" s="19" t="n">
         <f aca="false">F5-F7</f>
-        <v>0</v>
+        <v>195820.966771724</v>
       </c>
       <c r="G8" s="19" t="n">
         <f aca="false">G5-G7</f>
-        <v>0</v>
+        <v>220500.283213965</v>
       </c>
       <c r="H8" s="19" t="n">
         <f aca="false">H5-H7</f>
-        <v>0</v>
+        <v>244084.99350653</v>
       </c>
       <c r="I8" s="19" t="n">
         <f aca="false">I5-I7</f>
-        <v>0</v>
+        <v>265537.623585819</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4524,53 +4538,59 @@
         <v>130</v>
       </c>
       <c r="C9" s="16"/>
-      <c r="D9" s="20" t="str">
+      <c r="D9" s="20" t="n">
         <f aca="false">IFERROR(D8/D5,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E9" s="20" t="str">
+        <v>0.68920085883491</v>
+      </c>
+      <c r="E9" s="20" t="n">
         <f aca="false">IFERROR(E8/E5,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F9" s="20" t="str">
+        <v>0.697644438279714</v>
+      </c>
+      <c r="F9" s="20" t="n">
         <f aca="false">IFERROR(F8/F5,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G9" s="20" t="str">
+        <v>0.697644</v>
+      </c>
+      <c r="G9" s="20" t="n">
         <f aca="false">IFERROR(G8/G5,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H9" s="20" t="str">
+        <v>0.697644</v>
+      </c>
+      <c r="H9" s="20" t="n">
         <f aca="false">IFERROR(H8/H5,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I9" s="20" t="str">
+        <v>0.697644</v>
+      </c>
+      <c r="I9" s="20" t="n">
         <f aca="false">IFERROR(I8/I5,"-")</f>
-        <v>-</v>
+        <v>0.697644</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
+      <c r="C10" s="18" t="n">
+        <v>52237</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>57529</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>61575</v>
+      </c>
       <c r="F10" s="19" t="n">
         <f aca="false">F5*Assumptions!C7</f>
-        <v>0</v>
+        <v>70509.3467069507</v>
       </c>
       <c r="G10" s="19" t="n">
         <f aca="false">G5*Assumptions!D7</f>
-        <v>0</v>
+        <v>79395.6396724277</v>
       </c>
       <c r="H10" s="19" t="n">
         <f aca="false">H5*Assumptions!E7</f>
-        <v>0</v>
+        <v>87887.7972917906</v>
       </c>
       <c r="I10" s="19" t="n">
         <f aca="false">I5*Assumptions!F7</f>
-        <v>0</v>
+        <v>95612.255795766</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4582,19 +4602,19 @@
       <c r="E11" s="18"/>
       <c r="F11" s="19" t="n">
         <f aca="false">F8-F10</f>
-        <v>0</v>
+        <v>125311.620064774</v>
       </c>
       <c r="G11" s="19" t="n">
         <f aca="false">G8-G10</f>
-        <v>0</v>
+        <v>141104.643541537</v>
       </c>
       <c r="H11" s="19" t="n">
         <f aca="false">H8-H10</f>
-        <v>0</v>
+        <v>156197.19621474</v>
       </c>
       <c r="I11" s="19" t="n">
         <f aca="false">I8-I10</f>
-        <v>0</v>
+        <v>169925.367790053</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4604,21 +4624,21 @@
       <c r="C12" s="16"/>
       <c r="D12" s="16"/>
       <c r="E12" s="16"/>
-      <c r="F12" s="20" t="str">
+      <c r="F12" s="20" t="n">
         <f aca="false">IFERROR(F11/F5,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G12" s="20" t="str">
+        <v>0.446443</v>
+      </c>
+      <c r="G12" s="20" t="n">
         <f aca="false">IFERROR(G11/G5,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H12" s="20" t="str">
+        <v>0.446443</v>
+      </c>
+      <c r="H12" s="20" t="n">
         <f aca="false">IFERROR(H11/H5,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I12" s="20" t="str">
+        <v>0.446443</v>
+      </c>
+      <c r="I12" s="20" t="n">
         <f aca="false">IFERROR(I11/I5,"-")</f>
-        <v>-</v>
+        <v>0.446443</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4630,148 +4650,184 @@
       <c r="E13" s="18"/>
       <c r="F13" s="19" t="n">
         <f aca="false">F5*Assumptions!C10*Assumptions!C9</f>
-        <v>0</v>
+        <v>28011.7474361389</v>
       </c>
       <c r="G13" s="19" t="n">
         <f aca="false">G5*Assumptions!D10*Assumptions!D9</f>
-        <v>0</v>
+        <v>31542.0679655155</v>
       </c>
       <c r="H13" s="19" t="n">
         <f aca="false">H5*Assumptions!E10*Assumptions!E9</f>
-        <v>0</v>
+        <v>34915.8075551071</v>
       </c>
       <c r="I13" s="19" t="n">
         <f aca="false">I5*Assumptions!F10*Assumptions!F9</f>
-        <v>0</v>
+        <v>37984.5578811254</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
+      <c r="C14" s="18" t="n">
+        <v>83383</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>88523</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>109433</v>
+      </c>
       <c r="F14" s="19" t="n">
         <f aca="false">F11-F13</f>
-        <v>0</v>
+        <v>97299.8726286347</v>
       </c>
       <c r="G14" s="19" t="n">
         <f aca="false">G11-G13</f>
-        <v>0</v>
+        <v>109562.575576021</v>
       </c>
       <c r="H14" s="19" t="n">
         <f aca="false">H11-H13</f>
-        <v>0</v>
+        <v>121281.388659633</v>
       </c>
       <c r="I14" s="19" t="n">
         <f aca="false">I11-I13</f>
-        <v>0</v>
+        <v>131940.809908928</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
+      <c r="C15" s="18" t="n">
+        <v>2063</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>1968</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>2935</v>
+      </c>
       <c r="F15" s="19" t="n">
         <f aca="false">$E$15</f>
-        <v>0</v>
+        <v>2935</v>
       </c>
       <c r="G15" s="19" t="n">
         <f aca="false">$E$15</f>
-        <v>0</v>
+        <v>2935</v>
       </c>
       <c r="H15" s="19" t="n">
         <f aca="false">$E$15</f>
-        <v>0</v>
+        <v>2935</v>
       </c>
       <c r="I15" s="19" t="n">
         <f aca="false">$E$15</f>
-        <v>0</v>
+        <v>2935</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
+      <c r="C16" s="18" t="n">
+        <v>83716</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>89311</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>107787</v>
+      </c>
       <c r="F16" s="19" t="n">
         <f aca="false">F14-F15</f>
-        <v>0</v>
+        <v>94364.8726286347</v>
       </c>
       <c r="G16" s="19" t="n">
         <f aca="false">G14-G15</f>
-        <v>0</v>
+        <v>106627.575576021</v>
       </c>
       <c r="H16" s="19" t="n">
         <f aca="false">H14-H15</f>
-        <v>0</v>
+        <v>118346.388659633</v>
       </c>
       <c r="I16" s="19" t="n">
         <f aca="false">I14-I15</f>
-        <v>0</v>
+        <v>129005.809908928</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
+      <c r="C17" s="18" t="n">
+        <v>10978</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>16950</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>19651</v>
+      </c>
       <c r="F17" s="19" t="n">
         <f aca="false">F16*Assumptions!C8</f>
-        <v>0</v>
+        <v>17203.9430235443</v>
       </c>
       <c r="G17" s="19" t="n">
         <f aca="false">G16*Assumptions!D8</f>
-        <v>0</v>
+        <v>19439.5931859912</v>
       </c>
       <c r="H17" s="19" t="n">
         <f aca="false">H16*Assumptions!E8</f>
-        <v>0</v>
+        <v>21576.0851557036</v>
       </c>
       <c r="I17" s="19" t="n">
         <f aca="false">I16*Assumptions!F8</f>
-        <v>0</v>
+        <v>23519.4362219264</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
+      <c r="C18" s="18" t="n">
+        <v>72738</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>72361</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>88136</v>
+      </c>
       <c r="F18" s="19" t="n">
         <f aca="false">F16-F17</f>
-        <v>0</v>
+        <v>77160.9296050904</v>
       </c>
       <c r="G18" s="19" t="n">
         <f aca="false">G16-G17</f>
-        <v>0</v>
+        <v>87187.9823900303</v>
       </c>
       <c r="H18" s="19" t="n">
         <f aca="false">H16-H17</f>
-        <v>0</v>
+        <v>96770.3035039291</v>
       </c>
       <c r="I18" s="19" t="n">
         <f aca="false">I16-I17</f>
-        <v>0</v>
+        <v>105486.373687002</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
+      <c r="C19" s="18" t="n">
+        <v>7537.6</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>7475.3</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>7469.2</v>
+      </c>
       <c r="F19" s="19" t="n">
         <f aca="false">Assumptions!C12</f>
         <v>7400.1</v>
@@ -4793,24 +4849,30 @@
       <c r="B20" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
+      <c r="C20" s="18" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>11.8</v>
+      </c>
       <c r="F20" s="19" t="n">
         <f aca="false">IFERROR(F18/F19,"-")</f>
-        <v>0</v>
+        <v>10.4270117437724</v>
       </c>
       <c r="G20" s="19" t="n">
         <f aca="false">IFERROR(G18/G19,"-")</f>
-        <v>0</v>
+        <v>11.8359011715397</v>
       </c>
       <c r="H20" s="19" t="n">
         <f aca="false">IFERROR(H18/H19,"-")</f>
-        <v>0</v>
+        <v>13.1967302845981</v>
       </c>
       <c r="I20" s="19" t="n">
         <f aca="false">IFERROR(I18/I19,"-")</f>
-        <v>0</v>
+        <v>14.4511779830127</v>
       </c>
     </row>
   </sheetData>
@@ -5136,15 +5198,15 @@
       <c r="D5" s="19"/>
       <c r="E5" s="23" t="n">
         <f aca="false">IS!F18</f>
-        <v>0</v>
+        <v>77160.9296050904</v>
       </c>
       <c r="F5" s="23" t="n">
         <f aca="false">IS!G18</f>
-        <v>0</v>
+        <v>87187.9823900303</v>
       </c>
       <c r="G5" s="23" t="n">
         <f aca="false">IS!H18</f>
-        <v>0</v>
+        <v>96770.3035039291</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5155,15 +5217,15 @@
       <c r="D6" s="19"/>
       <c r="E6" s="23" t="n">
         <f aca="false">IS!F13</f>
-        <v>0</v>
+        <v>28011.7474361389</v>
       </c>
       <c r="F6" s="23" t="n">
         <f aca="false">IS!G13</f>
-        <v>0</v>
+        <v>31542.0679655155</v>
       </c>
       <c r="G6" s="23" t="n">
         <f aca="false">IS!H13</f>
-        <v>0</v>
+        <v>34915.8075551071</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5190,15 +5252,15 @@
       </c>
       <c r="E8" s="19" t="n">
         <f aca="false">E5+E6+E7</f>
-        <v>0</v>
+        <v>105172.677041229</v>
       </c>
       <c r="F8" s="19" t="n">
         <f aca="false">F5+F6+F7</f>
-        <v>0</v>
+        <v>118730.050355546</v>
       </c>
       <c r="G8" s="19" t="n">
         <f aca="false">G5+G6+G7</f>
-        <v>0</v>
+        <v>131686.111059036</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5225,15 +5287,15 @@
       </c>
       <c r="E10" s="19" t="n">
         <f aca="false">E8+E9</f>
-        <v>0</v>
+        <v>105172.677041229</v>
       </c>
       <c r="F10" s="19" t="n">
         <f aca="false">F8+F9</f>
-        <v>0</v>
+        <v>118730.050355546</v>
       </c>
       <c r="G10" s="19" t="n">
         <f aca="false">G8+G9</f>
-        <v>0</v>
+        <v>131686.111059036</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5270,15 +5332,15 @@
       </c>
       <c r="E13" s="19" t="n">
         <f aca="false">E10+E11+E12</f>
-        <v>0</v>
+        <v>105172.677041229</v>
       </c>
       <c r="F13" s="19" t="n">
         <f aca="false">F10+F11+F12</f>
-        <v>0</v>
+        <v>118730.050355546</v>
       </c>
       <c r="G13" s="19" t="n">
         <f aca="false">G10+G11+G12</f>
-        <v>0</v>
+        <v>131686.111059036</v>
       </c>
     </row>
   </sheetData>
@@ -5339,23 +5401,23 @@
       </c>
       <c r="C5" s="24" t="n">
         <f aca="false">IS!F14*(1-Assumptions!C8)+IS!F13-IS!F5*Assumptions!C10</f>
-        <v>0</v>
+        <v>56642.1385023404</v>
       </c>
       <c r="D5" s="24" t="n">
         <f aca="false">IS!G14*(1-Assumptions!D8)+IS!G13-IS!G5*Assumptions!D10</f>
-        <v>0</v>
+        <v>63780.7472177903</v>
       </c>
       <c r="E5" s="24" t="n">
         <f aca="false">IS!H14*(1-Assumptions!E8)+IS!H13-IS!H5*Assumptions!E10</f>
-        <v>0</v>
+        <v>70602.7359402052</v>
       </c>
       <c r="F5" s="24" t="n">
         <f aca="false">IS!I14*(1-Assumptions!F8)+IS!I13-IS!I5*Assumptions!F10</f>
-        <v>0</v>
+        <v>76808.0104019898</v>
       </c>
       <c r="G5" s="24" t="n">
         <f aca="false">F5*(1+Assumptions!G5)</f>
-        <v>0</v>
+        <v>82093.9376778548</v>
       </c>
       <c r="H5" s="0" t="s">
         <v>190</v>
@@ -5401,30 +5463,30 @@
       </c>
       <c r="C7" s="27" t="n">
         <f aca="false">C5*C6</f>
-        <v>0</v>
+        <v>52204.7359468575</v>
       </c>
       <c r="D7" s="27" t="n">
         <f aca="false">D5*D6</f>
-        <v>0</v>
+        <v>54178.8929200368</v>
       </c>
       <c r="E7" s="27" t="n">
         <f aca="false">E5*E6</f>
-        <v>0</v>
+        <v>55275.453738953</v>
       </c>
       <c r="F7" s="27" t="n">
         <f aca="false">F5*F6</f>
-        <v>0</v>
+        <v>55422.6851318613</v>
       </c>
       <c r="G7" s="27" t="n">
         <f aca="false">G5*G6</f>
-        <v>0</v>
+        <v>54596.1975323834</v>
       </c>
       <c r="H7" s="0" t="s">
         <v>194</v>
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">G5*(1+I6)/(I5-I6)</f>
-        <v>0</v>
+        <v>1402438.10199669</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5433,7 +5495,7 @@
       </c>
       <c r="I8" s="27" t="n">
         <f aca="false">I7*G6</f>
-        <v>0</v>
+        <v>932685.041178217</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5442,7 +5504,7 @@
       </c>
       <c r="I9" s="27" t="n">
         <f aca="false">SUM(C7:G7)</f>
-        <v>0</v>
+        <v>271677.965270092</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5451,7 +5513,7 @@
       </c>
       <c r="I10" s="28" t="n">
         <f aca="false">I8+I9</f>
-        <v>0</v>
+        <v>1204363.00644831</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5468,7 +5530,7 @@
       </c>
       <c r="I12" s="28" t="n">
         <f aca="false">I10-I11</f>
-        <v>8416</v>
+        <v>1212779.00644831</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5483,9 +5545,9 @@
       <c r="H14" s="0" t="s">
         <v>201</v>
       </c>
-      <c r="I14" s="28" t="str">
+      <c r="I14" s="28" t="n">
         <f aca="false">IF(OR(IS!E5="",IS!E5=0),"n/a - no forecast base",I12/I13)</f>
-        <v>n/a - no forecast base</v>
+        <v>163.139495083173</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5494,7 +5556,7 @@
       </c>
       <c r="I15" s="2" t="str">
         <f aca="false">IF(OR(IS!E5="",IS!E5=0),"MISSING - the DCF cannot value anything","present")</f>
-        <v>MISSING - the DCF cannot value anything</v>
+        <v>present</v>
       </c>
     </row>
   </sheetData>
